--- a/A_abtest实验配置.xlsx
+++ b/A_abtest实验配置.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\AOE-T+2release\common\excel\xls\Main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\projects\AOEM_server_trunk0921\NewKing\common\common\excel\xls\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8A93F3-176C-4CB0-AF1F-916AD71DBF61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410FEEC1-38AC-4B5D-A853-CA8BDFE29C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="杂项配置表" sheetId="1" r:id="rId1"/>
@@ -194,19 +194,19 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
+    <t>0~1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>"sceneConfId":"30015"</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
+    <t>2~9</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>"sceneConfId":"30012"</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>0~4</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>5~9</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -689,27 +689,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.26953125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="40.08984375" style="7" customWidth="1"/>
-    <col min="3" max="3" width="10.36328125" style="7" customWidth="1"/>
-    <col min="4" max="4" width="32.90625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="13.08984375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="23.6328125" style="7" customWidth="1"/>
-    <col min="7" max="7" width="34.08984375" style="7" customWidth="1"/>
-    <col min="8" max="8" width="25.7265625" style="7" customWidth="1"/>
-    <col min="9" max="9" width="20.453125" style="7" customWidth="1"/>
-    <col min="10" max="10" width="22.36328125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="12.25" style="7" customWidth="1"/>
+    <col min="2" max="2" width="40.125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="10.375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="32.875" style="7" customWidth="1"/>
+    <col min="5" max="5" width="13.125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="23.625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="34.125" style="7" customWidth="1"/>
+    <col min="8" max="8" width="25.75" style="7" customWidth="1"/>
+    <col min="9" max="9" width="20.5" style="7" customWidth="1"/>
+    <col min="10" max="10" width="22.375" style="7" customWidth="1"/>
     <col min="11" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -738,7 +738,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
@@ -767,7 +767,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -793,7 +793,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="F5" s="7">
         <v>2</v>
       </c>
@@ -801,7 +801,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" s="7">
         <v>2</v>
       </c>
@@ -827,7 +827,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="F7" s="7">
         <v>2</v>
       </c>
@@ -838,7 +838,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" s="7">
         <v>3</v>
       </c>
@@ -864,7 +864,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="F9" s="7">
         <v>2</v>
       </c>
@@ -875,7 +875,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" s="7">
         <v>4</v>
       </c>
@@ -901,7 +901,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="F11" s="7">
         <v>2</v>
       </c>
@@ -912,7 +912,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" s="7">
         <v>5</v>
       </c>
@@ -938,7 +938,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="F13" s="7">
         <v>2</v>
       </c>
@@ -949,7 +949,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" s="7">
         <v>6</v>
       </c>
@@ -975,7 +975,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" s="7">
         <v>7</v>
       </c>
@@ -995,21 +995,21 @@
         <v>1</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="F16" s="7">
         <v>2</v>
       </c>
       <c r="G16" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="12" t="s">
         <v>55</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1022,14 +1022,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="15.90625" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" customWidth="1"/>
+    <col min="1" max="1" width="15.875" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>44</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B3" s="2" t="s">
         <v>46</v>
       </c>
@@ -1048,7 +1048,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B4" s="2" t="s">
         <v>48</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B7" s="4" t="s">
         <v>14</v>
       </c>

--- a/A_abtest实验配置.xlsx
+++ b/A_abtest实验配置.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\projects\AOEM_server_trunk0921\NewKing\common\common\excel\xls\Main\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410FEEC1-38AC-4B5D-A853-CA8BDFE29C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="杂项配置表" sheetId="1" r:id="rId1"/>
@@ -34,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="57">
   <si>
     <t>convert(ResExp.proto, table_ExpLayerConf, ExpLayerConf.pbin)</t>
   </si>
@@ -168,6 +162,27 @@
     <t>elroysu-2024/10/12-场景礼包推荐实验</t>
   </si>
   <si>
+    <t>20241028_exp_inner_city_raid</t>
+  </si>
+  <si>
+    <t>peter-2024/10/28-内城新手副本蓝图</t>
+  </si>
+  <si>
+    <t>0~1</t>
+  </si>
+  <si>
+    <t>"sceneConfId":"30015"</t>
+  </si>
+  <si>
+    <t>111111111111</t>
+  </si>
+  <si>
+    <t>2~9</t>
+  </si>
+  <si>
+    <t>"sceneConfId":"30012"</t>
+  </si>
+  <si>
     <t>ExpHashRule</t>
   </si>
   <si>
@@ -184,37 +199,19 @@
   </si>
   <si>
     <t>uid哈希100</t>
-  </si>
-  <si>
-    <t>20241028_exp_inner_city_raid</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>peter-2024/10/28-内城新手副本蓝图</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>0~1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>"sceneConfId":"30015"</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>2~9</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>"sceneConfId":"30012"</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -263,27 +260,135 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Microsoft YaHei UI"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -316,12 +421,174 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -359,21 +626,221 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -381,22 +848,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="23">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="24">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="19">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -405,34 +872,77 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="24" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="5">
-    <cellStyle name="差" xfId="3" builtinId="27"/>
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="检查单元格" xfId="2" builtinId="23"/>
-    <cellStyle name="适中" xfId="4" builtinId="28"/>
-    <cellStyle name="输入" xfId="1" builtinId="20"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -682,14 +1192,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.25" style="7" customWidth="1"/>
     <col min="2" max="2" width="40.125" style="7" customWidth="1"/>
@@ -704,12 +1214,12 @@
     <col min="11" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" s="5" customFormat="1" spans="1:1">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="2" s="6" customFormat="1" ht="15" spans="1:10">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -738,7 +1248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="3" s="4" customFormat="1" ht="15.75" spans="1:10">
       <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
@@ -767,7 +1277,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" ht="15" spans="1:8">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -793,7 +1303,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="6:8">
       <c r="F5" s="7">
         <v>2</v>
       </c>
@@ -801,7 +1311,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:8">
       <c r="A6" s="7">
         <v>2</v>
       </c>
@@ -827,7 +1337,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="6:8">
       <c r="F7" s="7">
         <v>2</v>
       </c>
@@ -838,7 +1348,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:8">
       <c r="A8" s="7">
         <v>3</v>
       </c>
@@ -864,7 +1374,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="6:8">
       <c r="F9" s="7">
         <v>2</v>
       </c>
@@ -875,7 +1385,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:8">
       <c r="A10" s="7">
         <v>4</v>
       </c>
@@ -901,7 +1411,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="6:8">
       <c r="F11" s="7">
         <v>2</v>
       </c>
@@ -912,7 +1422,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:8">
       <c r="A12" s="7">
         <v>5</v>
       </c>
@@ -938,7 +1448,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="6:8">
       <c r="F13" s="7">
         <v>2</v>
       </c>
@@ -949,7 +1459,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:8">
       <c r="A14" s="7">
         <v>6</v>
       </c>
@@ -975,18 +1485,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:8">
       <c r="A15" s="7">
         <v>7</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>20</v>
@@ -995,68 +1505,115 @@
         <v>1</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="7">
+        <v>8</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>48</v>
+      </c>
       <c r="F16" s="7">
         <v>2</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>55</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="7">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>22222222222</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="7">
+        <v>10</v>
+      </c>
+      <c r="C18" s="7">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="7">
+        <v>11</v>
+      </c>
+      <c r="C19" s="7">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="7">
+        <v>12</v>
+      </c>
+      <c r="C20" s="7">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="7">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="15.875" customWidth="1"/>
     <col min="2" max="2" width="16.25" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="1" ht="14.25"/>
+    <row r="2" ht="15" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" ht="15" spans="2:3">
       <c r="B3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" ht="15" spans="2:3">
       <c r="B4" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25"/>
+    <row r="6" ht="14.25"/>
+    <row r="7" ht="15.75" spans="2:5">
       <c r="B7" s="4" t="s">
         <v>14</v>
       </c>
@@ -1070,8 +1627,9 @@
         <v>17</v>
       </c>
     </row>
+    <row r="8" ht="14.25"/>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/A_abtest实验配置.xlsx
+++ b/A_abtest实验配置.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="55">
   <si>
     <t>convert(ResExp.proto, table_ExpLayerConf, ExpLayerConf.pbin)</t>
   </si>
@@ -99,9 +99,6 @@
     <t>"scene" : "A"</t>
   </si>
   <si>
-    <t xml:space="preserve">"scene" : "B" </t>
-  </si>
-  <si>
     <t>20240422_exp_raid_newbie_tapgroundtutorial</t>
   </si>
   <si>
@@ -114,19 +111,16 @@
     <t>"scene" : "drag_avatar"</t>
   </si>
   <si>
+    <t>20240422_exp_raid_newbie_fixcameratutorial</t>
+  </si>
+  <si>
+    <t>peter-2024/04/22-固定跟随镜头操作</t>
+  </si>
+  <si>
+    <t>"scene" : "nonfix"</t>
+  </si>
+  <si>
     <t>5~9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"scene" : "tap_ground" </t>
-  </si>
-  <si>
-    <t>20240422_exp_raid_newbie_fixcameratutorial</t>
-  </si>
-  <si>
-    <t>peter-2024/04/22-固定跟随镜头操作</t>
-  </si>
-  <si>
-    <t>"scene" : "nonfix"</t>
   </si>
   <si>
     <t xml:space="preserve">"scene" : "fix" </t>
@@ -211,7 +205,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,12 +250,6 @@
     <font>
       <sz val="9"/>
       <color theme="2"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
       <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
@@ -714,55 +702,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -771,80 +759,80 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -876,12 +864,6 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
@@ -1198,7 +1180,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.25" style="7" customWidth="1"/>
@@ -1303,26 +1285,44 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="6:8">
+    <row r="5" spans="1:8">
+      <c r="A5" s="7">
+        <v>2</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="7">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="F5" s="7">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C6" s="7">
         <v>1</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>20</v>
@@ -1331,10 +1331,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="6:8">
@@ -1342,24 +1342,24 @@
         <v>2</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" s="7">
         <v>1</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>20</v>
@@ -1368,10 +1368,10 @@
         <v>1</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="6:8">
@@ -1379,24 +1379,24 @@
         <v>2</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C10" s="7">
         <v>1</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>20</v>
@@ -1405,10 +1405,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="6:8">
@@ -1416,24 +1416,24 @@
         <v>2</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C12" s="7">
         <v>1</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>20</v>
@@ -1442,126 +1442,89 @@
         <v>1</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="6:8">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="7">
+        <v>7</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="F13" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="7">
-        <v>6</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="7">
-        <v>1</v>
-      </c>
-      <c r="D14" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="7">
+        <v>2</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="7">
+        <v>9</v>
+      </c>
+      <c r="B15" s="7">
+        <v>22222222222</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="7">
+        <v>10</v>
+      </c>
+      <c r="C16" s="7">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="7">
+        <v>11</v>
+      </c>
+      <c r="C17" s="7">
         <v>43</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="7">
-        <v>1</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="7">
-        <v>7</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="7">
-        <v>1</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="7">
-        <v>1</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="7">
-        <v>8</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="7">
-        <v>2</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="7">
-        <v>9</v>
-      </c>
-      <c r="B17" s="7">
-        <v>22222222222</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C18" s="7">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
       <c r="A19" s="7">
-        <v>11</v>
-      </c>
-      <c r="C19" s="7">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="7">
-        <v>12</v>
-      </c>
-      <c r="C20" s="7">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="7">
         <v>13</v>
       </c>
     </row>
@@ -1586,29 +1549,29 @@
     <row r="1" ht="14.25"/>
     <row r="2" ht="15" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" ht="15" spans="2:3">
       <c r="B3" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" ht="15" spans="2:3">
       <c r="B4" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" ht="14.25"/>
